--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.43219782356111</v>
+        <v>8.68273214632868</v>
       </c>
       <c r="D2" t="n">
-        <v>53.16581659071796</v>
+        <v>8.639445195991669</v>
       </c>
       <c r="E2" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F2" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.29752741075266</v>
+        <v>9.148348204247307</v>
       </c>
       <c r="D3" t="n">
-        <v>56.09016288819901</v>
+        <v>9.11465146933234</v>
       </c>
       <c r="E3" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F3" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.40330921647817</v>
+        <v>6.240537747677703</v>
       </c>
       <c r="D4" t="n">
-        <v>38.2161670502324</v>
+        <v>6.210127145662765</v>
       </c>
       <c r="E4" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F4" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.70426339655501</v>
+        <v>6.776942801940189</v>
       </c>
       <c r="D5" t="n">
-        <v>41.56439484508149</v>
+        <v>6.754214162325743</v>
       </c>
       <c r="E5" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F5" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.15923712130368</v>
+        <v>3.438376032211849</v>
       </c>
       <c r="D6" t="n">
-        <v>24.91839474728547</v>
+        <v>4.049239146433889</v>
       </c>
       <c r="E6" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.49456718218917</v>
+        <v>8.04286716710574</v>
       </c>
       <c r="D7" t="n">
-        <v>49.3519307174755</v>
+        <v>8.019688741589768</v>
       </c>
       <c r="E7" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.414980616018282</v>
+        <v>1.529934350102971</v>
       </c>
       <c r="D8" t="n">
-        <v>12.89474126473424</v>
+        <v>2.095395455519314</v>
       </c>
       <c r="E8" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F8" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.04776806524635</v>
+        <v>6.832762310602533</v>
       </c>
       <c r="D9" t="n">
-        <v>42.16043964195097</v>
+        <v>6.851071441817032</v>
       </c>
       <c r="E9" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.82755921171191</v>
+        <v>5.984478371903187</v>
       </c>
       <c r="D10" t="n">
-        <v>36.98911330304161</v>
+        <v>6.010730911744261</v>
       </c>
       <c r="E10" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.01899220622455</v>
+        <v>3.57808623351149</v>
       </c>
       <c r="D11" t="n">
-        <v>18.30247076683079</v>
+        <v>2.974151499610004</v>
       </c>
       <c r="E11" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F11" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.85683714332612</v>
+        <v>6.151736035790496</v>
       </c>
       <c r="D12" t="n">
-        <v>38.13107907939185</v>
+        <v>6.196300350401176</v>
       </c>
       <c r="E12" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F12" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.68579452141218</v>
+        <v>7.748941609729481</v>
       </c>
       <c r="D13" t="n">
-        <v>47.84744160319669</v>
+        <v>7.775209260519463</v>
       </c>
       <c r="E13" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F13" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.84132627787007</v>
+        <v>5.499215520153886</v>
       </c>
       <c r="D14" t="n">
-        <v>30.08209132633084</v>
+        <v>4.888339840528762</v>
       </c>
       <c r="E14" t="n">
-        <v>13.01725945283922</v>
+        <v>2.115304661086373</v>
       </c>
       <c r="F14" t="n">
-        <v>12.6030211308903</v>
+        <v>2.047990933769675</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
